--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2832,6 +2832,1352 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129521348</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92870</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>480472</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6596483</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129521667</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>480457</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6596668</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129521288</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92870</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>480473</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6596476</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129521154</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92870</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>480481</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6596464</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129522345</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>480276</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6596837</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Framlockade. Fotografier.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129524102</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>480493</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6596518</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Framlockade tillsammans med tofsmes. Video.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129522083</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>480299</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6596831</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129521781</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>480370</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6596683</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129522042</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>480333</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6596894</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129521873</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97345</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>480377</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6596794</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129522031</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>480331</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6596895</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129522408</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>480284</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6596815</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -3645,7 +3645,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129521781</v>
+        <v>129522042</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3676,14 +3676,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480370</v>
+        <v>480333</v>
       </c>
       <c r="R27" t="n">
-        <v>6596683</v>
+        <v>6596894</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3752,7 +3752,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129522042</v>
+        <v>129521781</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3783,14 +3783,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480333</v>
+        <v>480370</v>
       </c>
       <c r="R28" t="n">
-        <v>6596894</v>
+        <v>6596683</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -2837,7 +2837,7 @@
         <v>129521348</v>
       </c>
       <c r="B20" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>129521288</v>
       </c>
       <c r="B22" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>129521154</v>
       </c>
       <c r="B23" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129522042</v>
+        <v>129521781</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3676,14 +3676,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480333</v>
+        <v>480370</v>
       </c>
       <c r="R27" t="n">
-        <v>6596894</v>
+        <v>6596683</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3752,7 +3752,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129521781</v>
+        <v>129522042</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3783,14 +3783,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480370</v>
+        <v>480333</v>
       </c>
       <c r="R28" t="n">
-        <v>6596683</v>
+        <v>6596894</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3862,7 +3862,7 @@
         <v>129521873</v>
       </c>
       <c r="B29" t="n">
-        <v>97345</v>
+        <v>97348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -2941,10 +2941,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129521667</v>
+        <v>129521288</v>
       </c>
       <c r="B21" t="n">
-        <v>56908</v>
+        <v>92873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,48 +2952,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480457</v>
+        <v>480473</v>
       </c>
       <c r="R21" t="n">
-        <v>6596668</v>
+        <v>6596476</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3025,7 +3011,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3035,7 +3021,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3062,7 +3048,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129521288</v>
+        <v>129521154</v>
       </c>
       <c r="B22" t="n">
         <v>92873</v>
@@ -3097,10 +3083,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480473</v>
+        <v>480481</v>
       </c>
       <c r="R22" t="n">
-        <v>6596476</v>
+        <v>6596464</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3132,7 +3118,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3142,7 +3128,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3169,10 +3155,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129521154</v>
+        <v>129522083</v>
       </c>
       <c r="B23" t="n">
-        <v>92873</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3180,34 +3166,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480481</v>
+        <v>480299</v>
       </c>
       <c r="R23" t="n">
-        <v>6596464</v>
+        <v>6596831</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3239,7 +3225,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3249,7 +3235,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3276,10 +3262,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129522345</v>
+        <v>129521781</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,53 +3273,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480276</v>
+        <v>480370</v>
       </c>
       <c r="R24" t="n">
-        <v>6596837</v>
+        <v>6596683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3365,7 +3332,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3375,12 +3342,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Framlockade. Fotografier.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,10 +3369,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129524102</v>
+        <v>129522042</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3418,53 +3380,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480493</v>
+        <v>480333</v>
       </c>
       <c r="R25" t="n">
-        <v>6596518</v>
+        <v>6596894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3496,7 +3439,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3506,12 +3449,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Framlockade tillsammans med tofsmes. Video.</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3538,45 +3476,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129522083</v>
+        <v>129521873</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>97348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480299</v>
+        <v>480377</v>
       </c>
       <c r="R26" t="n">
-        <v>6596831</v>
+        <v>6596794</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3608,7 +3546,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3618,7 +3556,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3645,7 +3583,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129522042</v>
+        <v>129522031</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3680,10 +3618,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480333</v>
+        <v>480331</v>
       </c>
       <c r="R27" t="n">
-        <v>6596894</v>
+        <v>6596895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,7 +3653,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3725,7 +3663,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3752,7 +3690,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129521781</v>
+        <v>129522408</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3783,14 +3721,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480370</v>
+        <v>480284</v>
       </c>
       <c r="R28" t="n">
-        <v>6596683</v>
+        <v>6596815</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3822,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3832,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3859,45 +3797,59 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129521873</v>
+        <v>129521667</v>
       </c>
       <c r="B29" t="n">
-        <v>97348</v>
+        <v>56908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2569</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480377</v>
+        <v>480457</v>
       </c>
       <c r="R29" t="n">
-        <v>6596794</v>
+        <v>6596668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3929,7 +3881,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3939,7 +3891,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3966,10 +3918,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129522031</v>
+        <v>129522345</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3977,34 +3929,53 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480331</v>
+        <v>480276</v>
       </c>
       <c r="R30" t="n">
-        <v>6596895</v>
+        <v>6596837</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4036,7 +4007,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4046,7 +4017,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Framlockade. Fotografier.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4073,10 +4049,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129522408</v>
+        <v>129524102</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4084,34 +4060,53 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480284</v>
+        <v>480493</v>
       </c>
       <c r="R31" t="n">
-        <v>6596815</v>
+        <v>6596518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4143,7 +4138,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4153,7 +4148,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Framlockade tillsammans med tofsmes. Video.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -2837,7 +2837,7 @@
         <v>129521348</v>
       </c>
       <c r="B20" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>129521288</v>
       </c>
       <c r="B21" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129521154</v>
       </c>
       <c r="B22" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>129522083</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>129521781</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129522042</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>129521873</v>
       </c>
       <c r="B26" t="n">
-        <v>97348</v>
+        <v>97377</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>129522031</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129522408</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>129521667</v>
       </c>
       <c r="B29" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>129522345</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>129524102</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -2837,7 +2837,7 @@
         <v>129521348</v>
       </c>
       <c r="B20" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>129521288</v>
       </c>
       <c r="B21" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129521154</v>
       </c>
       <c r="B22" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>129522083</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>129521781</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129522042</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>129521873</v>
       </c>
       <c r="B26" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>129522031</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129522408</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>129521667</v>
       </c>
       <c r="B29" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>129522345</v>
       </c>
       <c r="B30" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>129524102</v>
       </c>
       <c r="B31" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -2837,7 +2837,7 @@
         <v>129521348</v>
       </c>
       <c r="B20" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>129521288</v>
       </c>
       <c r="B21" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129521154</v>
       </c>
       <c r="B22" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>129522083</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>129521781</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129522042</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>129521873</v>
       </c>
       <c r="B26" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>129522031</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129522408</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>129521667</v>
       </c>
       <c r="B29" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>129522345</v>
       </c>
       <c r="B30" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>129524102</v>
       </c>
       <c r="B31" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -2837,7 +2837,7 @@
         <v>129521348</v>
       </c>
       <c r="B20" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>129521288</v>
       </c>
       <c r="B21" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129521154</v>
       </c>
       <c r="B22" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>129522083</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129521781</v>
+        <v>129522042</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3293,14 +3293,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480370</v>
+        <v>480333</v>
       </c>
       <c r="R24" t="n">
-        <v>6596683</v>
+        <v>6596894</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129522042</v>
+        <v>129521781</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,14 +3400,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480333</v>
+        <v>480370</v>
       </c>
       <c r="R25" t="n">
-        <v>6596894</v>
+        <v>6596683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3479,7 +3479,7 @@
         <v>129521873</v>
       </c>
       <c r="B26" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>129522031</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129522408</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -3262,7 +3262,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129522042</v>
+        <v>129521781</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3293,14 +3293,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480333</v>
+        <v>480370</v>
       </c>
       <c r="R24" t="n">
-        <v>6596894</v>
+        <v>6596683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129521781</v>
+        <v>129522042</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3400,14 +3400,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480370</v>
+        <v>480333</v>
       </c>
       <c r="R25" t="n">
-        <v>6596683</v>
+        <v>6596894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -2837,7 +2837,7 @@
         <v>129521348</v>
       </c>
       <c r="B20" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>129521288</v>
       </c>
       <c r="B21" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129521154</v>
       </c>
       <c r="B22" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129521781</v>
+        <v>129522042</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3293,14 +3293,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480370</v>
+        <v>480333</v>
       </c>
       <c r="R24" t="n">
-        <v>6596683</v>
+        <v>6596894</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129522042</v>
+        <v>129521781</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3400,14 +3400,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480333</v>
+        <v>480370</v>
       </c>
       <c r="R25" t="n">
-        <v>6596894</v>
+        <v>6596683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3479,7 +3479,7 @@
         <v>129521873</v>
       </c>
       <c r="B26" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -2837,7 +2837,7 @@
         <v>129521348</v>
       </c>
       <c r="B20" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>129521288</v>
       </c>
       <c r="B21" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129521154</v>
       </c>
       <c r="B22" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129522042</v>
+        <v>129521781</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3293,14 +3293,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480333</v>
+        <v>480370</v>
       </c>
       <c r="R24" t="n">
-        <v>6596894</v>
+        <v>6596683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129521781</v>
+        <v>129522042</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3400,14 +3400,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480370</v>
+        <v>480333</v>
       </c>
       <c r="R25" t="n">
-        <v>6596683</v>
+        <v>6596894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3479,7 +3479,7 @@
         <v>129521873</v>
       </c>
       <c r="B26" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -3479,7 +3479,7 @@
         <v>129521873</v>
       </c>
       <c r="B26" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -3262,7 +3262,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129521781</v>
+        <v>129522042</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3293,14 +3293,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480370</v>
+        <v>480333</v>
       </c>
       <c r="R24" t="n">
-        <v>6596683</v>
+        <v>6596894</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129522042</v>
+        <v>129521781</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3400,14 +3400,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480333</v>
+        <v>480370</v>
       </c>
       <c r="R25" t="n">
-        <v>6596894</v>
+        <v>6596683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -3800,7 +3800,7 @@
         <v>129521667</v>
       </c>
       <c r="B29" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>129522345</v>
       </c>
       <c r="B30" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>129524102</v>
       </c>
       <c r="B31" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -3800,7 +3800,7 @@
         <v>129521667</v>
       </c>
       <c r="B29" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>129522345</v>
       </c>
       <c r="B30" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>129524102</v>
       </c>
       <c r="B31" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4178,6 +4178,107 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130799135</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>480353</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6596838</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4183,7 +4183,7 @@
         <v>130799135</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4183,7 +4183,7 @@
         <v>130799135</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4279,6 +4279,133 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131355405</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>480466</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6596567</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4405,6 +4405,1686 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131810081</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>480313</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6596805</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131812897</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>480272</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6596657</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131811868</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>480325</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6596655</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringbarkning i död tall med fläkbark.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131813198</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79883</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>480351</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6596553</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131813900</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>480353</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6596484</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringbarkning i nyligen död tall med fläkbark.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131810538</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>480263</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6596738</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På grov tallåga.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131808004</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>480375</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6596722</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bohål i tallöverståndare lämpliga för pärluggla.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131813043</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79883</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>480308</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6596608</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131810287</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>480265</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6596773</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringbarkning i sakta döende tall.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131809976</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>480301</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6596807</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131810858</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>480328</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6596728</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök i sakta döende stavatall.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131806959</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>480467</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6596512</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131807177</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>480453</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6596568</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Filmsnutt finns sparad.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131814360</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>480297</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6596424</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4408,32 +4408,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131810081</v>
+        <v>131812897</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480313</v>
+        <v>480272</v>
       </c>
       <c r="R34" t="n">
-        <v>6596805</v>
+        <v>6596657</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131812897</v>
+        <v>131810081</v>
       </c>
       <c r="B35" t="n">
-        <v>91795</v>
+        <v>79264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480272</v>
+        <v>480313</v>
       </c>
       <c r="R35" t="n">
-        <v>6596657</v>
+        <v>6596805</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,32 +4408,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131812897</v>
+        <v>131810081</v>
       </c>
       <c r="B34" t="n">
-        <v>91795</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480272</v>
+        <v>480313</v>
       </c>
       <c r="R34" t="n">
-        <v>6596657</v>
+        <v>6596805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131810081</v>
+        <v>131812897</v>
       </c>
       <c r="B35" t="n">
-        <v>79264</v>
+        <v>91801</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480313</v>
+        <v>480272</v>
       </c>
       <c r="R35" t="n">
-        <v>6596805</v>
+        <v>6596657</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4625,7 +4625,7 @@
         <v>131811868</v>
       </c>
       <c r="B36" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>131813198</v>
       </c>
       <c r="B37" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>131813900</v>
       </c>
       <c r="B38" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>131810538</v>
       </c>
       <c r="B39" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>131808004</v>
       </c>
       <c r="B40" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>131813043</v>
       </c>
       <c r="B41" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>131810287</v>
       </c>
       <c r="B42" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>131809976</v>
       </c>
       <c r="B43" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131810858</v>
       </c>
       <c r="B44" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>131806959</v>
       </c>
       <c r="B45" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>131807177</v>
       </c>
       <c r="B46" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>131814360</v>
       </c>
       <c r="B47" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4408,32 +4408,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131810081</v>
+        <v>131812897</v>
       </c>
       <c r="B34" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480313</v>
+        <v>480272</v>
       </c>
       <c r="R34" t="n">
-        <v>6596805</v>
+        <v>6596657</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131812897</v>
+        <v>131810081</v>
       </c>
       <c r="B35" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480272</v>
+        <v>480313</v>
       </c>
       <c r="R35" t="n">
-        <v>6596657</v>
+        <v>6596805</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4622,10 +4622,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131811868</v>
+        <v>131813198</v>
       </c>
       <c r="B36" t="n">
-        <v>57904</v>
+        <v>79885</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,48 +4633,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480325</v>
+        <v>480351</v>
       </c>
       <c r="R36" t="n">
-        <v>6596655</v>
+        <v>6596553</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4706,7 +4692,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4716,12 +4702,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringbarkning i död tall med fläkbark.</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4748,7 +4729,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131813198</v>
+        <v>131813043</v>
       </c>
       <c r="B37" t="n">
         <v>79885</v>
@@ -4783,10 +4764,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480351</v>
+        <v>480308</v>
       </c>
       <c r="R37" t="n">
-        <v>6596553</v>
+        <v>6596608</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4818,7 +4799,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4828,7 +4809,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,10 +4836,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131813900</v>
+        <v>131809976</v>
       </c>
       <c r="B38" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4866,48 +4847,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480353</v>
+        <v>480301</v>
       </c>
       <c r="R38" t="n">
-        <v>6596484</v>
+        <v>6596807</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4939,7 +4906,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4949,12 +4916,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringbarkning i nyligen död tall med fläkbark.</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4981,32 +4943,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131810538</v>
+        <v>131811868</v>
       </c>
       <c r="B39" t="n">
-        <v>57092</v>
+        <v>57905</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5019,14 +4981,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5035,10 +4992,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480263</v>
+        <v>480325</v>
       </c>
       <c r="R39" t="n">
-        <v>6596738</v>
+        <v>6596655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5070,7 +5027,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5080,12 +5037,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På grov tallåga.</t>
+          <t>Ringbarkning i död tall med fläkbark.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5112,10 +5069,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131808004</v>
+        <v>131813900</v>
       </c>
       <c r="B40" t="n">
-        <v>57901</v>
+        <v>57905</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,16 +5080,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5152,7 +5109,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5161,10 +5118,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480375</v>
+        <v>480353</v>
       </c>
       <c r="R40" t="n">
-        <v>6596722</v>
+        <v>6596484</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5196,7 +5153,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5206,12 +5163,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare lämpliga för pärluggla.</t>
+          <t>Ringbarkning i nyligen död tall med fläkbark.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5238,45 +5195,64 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131813043</v>
+        <v>131810538</v>
       </c>
       <c r="B41" t="n">
-        <v>79885</v>
+        <v>57093</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480308</v>
+        <v>480263</v>
       </c>
       <c r="R41" t="n">
-        <v>6596608</v>
+        <v>6596738</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5308,7 +5284,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5318,7 +5294,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På grov tallåga.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5345,10 +5326,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131810287</v>
+        <v>131808004</v>
       </c>
       <c r="B42" t="n">
-        <v>57904</v>
+        <v>57902</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,16 +5337,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5385,7 +5366,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5394,10 +5375,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480265</v>
+        <v>480375</v>
       </c>
       <c r="R42" t="n">
-        <v>6596773</v>
+        <v>6596722</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5429,7 +5410,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5439,12 +5420,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringbarkning i sakta döende tall.</t>
+          <t>Bohål i tallöverståndare lämpliga för pärluggla.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5471,10 +5452,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131809976</v>
+        <v>131810287</v>
       </c>
       <c r="B43" t="n">
-        <v>79266</v>
+        <v>57905</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,34 +5463,48 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480301</v>
+        <v>480265</v>
       </c>
       <c r="R43" t="n">
-        <v>6596807</v>
+        <v>6596773</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5541,7 +5536,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5551,7 +5546,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringbarkning i sakta döende tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5581,7 +5581,7 @@
         <v>131810858</v>
       </c>
       <c r="B44" t="n">
-        <v>57904</v>
+        <v>57905</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>131806959</v>
       </c>
       <c r="B45" t="n">
-        <v>57092</v>
+        <v>57093</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>131807177</v>
       </c>
       <c r="B46" t="n">
-        <v>58063</v>
+        <v>58064</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>131814360</v>
       </c>
       <c r="B47" t="n">
-        <v>57092</v>
+        <v>57093</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4408,32 +4408,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131812897</v>
+        <v>131810081</v>
       </c>
       <c r="B34" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480272</v>
+        <v>480313</v>
       </c>
       <c r="R34" t="n">
-        <v>6596657</v>
+        <v>6596805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131810081</v>
+        <v>131812897</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480313</v>
+        <v>480272</v>
       </c>
       <c r="R35" t="n">
-        <v>6596805</v>
+        <v>6596657</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,32 +4408,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131810081</v>
+        <v>131812897</v>
       </c>
       <c r="B34" t="n">
-        <v>79266</v>
+        <v>91804</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480313</v>
+        <v>480272</v>
       </c>
       <c r="R34" t="n">
-        <v>6596805</v>
+        <v>6596657</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131812897</v>
+        <v>131810081</v>
       </c>
       <c r="B35" t="n">
-        <v>91801</v>
+        <v>79269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480272</v>
+        <v>480313</v>
       </c>
       <c r="R35" t="n">
-        <v>6596657</v>
+        <v>6596805</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4625,7 +4625,7 @@
         <v>131813198</v>
       </c>
       <c r="B36" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>131813043</v>
       </c>
       <c r="B37" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>131809976</v>
       </c>
       <c r="B38" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>131811868</v>
       </c>
       <c r="B39" t="n">
-        <v>57905</v>
+        <v>57907</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>131813900</v>
       </c>
       <c r="B40" t="n">
-        <v>57905</v>
+        <v>57907</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>131810538</v>
       </c>
       <c r="B41" t="n">
-        <v>57093</v>
+        <v>57095</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>131808004</v>
       </c>
       <c r="B42" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>131810287</v>
       </c>
       <c r="B43" t="n">
-        <v>57905</v>
+        <v>57907</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131810858</v>
       </c>
       <c r="B44" t="n">
-        <v>57905</v>
+        <v>57907</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>131806959</v>
       </c>
       <c r="B45" t="n">
-        <v>57093</v>
+        <v>57095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>131807177</v>
       </c>
       <c r="B46" t="n">
-        <v>58064</v>
+        <v>58066</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>131814360</v>
       </c>
       <c r="B47" t="n">
-        <v>57093</v>
+        <v>57095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4284,7 +4284,7 @@
         <v>131355405</v>
       </c>
       <c r="B33" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>131812897</v>
       </c>
       <c r="B34" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>131810081</v>
       </c>
       <c r="B35" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>131813198</v>
       </c>
       <c r="B36" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>131813043</v>
       </c>
       <c r="B37" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>131809976</v>
       </c>
       <c r="B38" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>131811868</v>
       </c>
       <c r="B39" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>131813900</v>
       </c>
       <c r="B40" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>131810538</v>
       </c>
       <c r="B41" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>131808004</v>
       </c>
       <c r="B42" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>131810287</v>
       </c>
       <c r="B43" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131810858</v>
       </c>
       <c r="B44" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>131806959</v>
       </c>
       <c r="B45" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>131807177</v>
       </c>
       <c r="B46" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>131814360</v>
       </c>
       <c r="B47" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4408,32 +4408,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131810081</v>
+        <v>131812897</v>
       </c>
       <c r="B34" t="n">
-        <v>79315</v>
+        <v>91855</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480313</v>
+        <v>480272</v>
       </c>
       <c r="R34" t="n">
-        <v>6596805</v>
+        <v>6596657</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131812897</v>
+        <v>131810081</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480272</v>
+        <v>480313</v>
       </c>
       <c r="R35" t="n">
-        <v>6596657</v>
+        <v>6596805</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4625,7 +4625,7 @@
         <v>131813198</v>
       </c>
       <c r="B36" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>131813043</v>
       </c>
       <c r="B37" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>131809976</v>
       </c>
       <c r="B38" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>131807177</v>
       </c>
       <c r="B46" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>131811868</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>131813900</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>131810538</v>
       </c>
       <c r="B41" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>131808004</v>
       </c>
       <c r="B42" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>131810287</v>
       </c>
       <c r="B43" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131810858</v>
       </c>
       <c r="B44" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>131806959</v>
       </c>
       <c r="B45" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>131807177</v>
       </c>
       <c r="B46" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>131814360</v>
       </c>
       <c r="B47" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>131811868</v>
       </c>
       <c r="B39" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>131813900</v>
       </c>
       <c r="B40" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>131810538</v>
       </c>
       <c r="B41" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>131808004</v>
       </c>
       <c r="B42" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>131810287</v>
       </c>
       <c r="B43" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131810858</v>
       </c>
       <c r="B44" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>131806959</v>
       </c>
       <c r="B45" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>131807177</v>
       </c>
       <c r="B46" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>131814360</v>
       </c>
       <c r="B47" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -6091,7 +6091,7 @@
         <v>133024889</v>
       </c>
       <c r="B48" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -6091,7 +6091,7 @@
         <v>133024889</v>
       </c>
       <c r="B48" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335149</v>
+        <v>122335159</v>
       </c>
       <c r="B2" t="n">
-        <v>78396</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480442</v>
+        <v>480354</v>
       </c>
       <c r="R2" t="n">
-        <v>6596485</v>
+        <v>6596544</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,56 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335159</v>
+        <v>129521873</v>
       </c>
       <c r="B3" t="n">
-        <v>78305</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480354</v>
+        <v>480377</v>
       </c>
       <c r="R3" t="n">
-        <v>6596544</v>
+        <v>6596794</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,83 +865,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335205</v>
+        <v>131812897</v>
       </c>
       <c r="B4" t="n">
-        <v>78823</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480539</v>
+        <v>480272</v>
       </c>
       <c r="R4" t="n">
-        <v>6596612</v>
+        <v>6596657</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,17 +948,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,34 +972,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335213</v>
+        <v>133024889</v>
       </c>
       <c r="B5" t="n">
-        <v>78749</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,40 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480554</v>
+        <v>480357</v>
       </c>
       <c r="R5" t="n">
-        <v>6596596</v>
+        <v>6596841</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1055,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,92 +1079,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122335180</v>
+        <v>62161729</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Kring sjön Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480403</v>
+        <v>480199</v>
       </c>
       <c r="R6" t="n">
-        <v>6596616</v>
+        <v>6596741</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,12 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2016-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2016-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,31 +1178,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hällmarkskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123991709</v>
+        <v>129521288</v>
       </c>
       <c r="B7" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480553</v>
+        <v>480473</v>
       </c>
       <c r="R7" t="n">
-        <v>6596500</v>
+        <v>6596476</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,22 +1264,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,15 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123988405</v>
+        <v>129521331</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,34 +1317,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480313</v>
+        <v>480472</v>
       </c>
       <c r="R8" t="n">
-        <v>6596806</v>
+        <v>6596483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,22 +1371,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,16 +1416,11 @@
         <v>123987634</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1575,60 +1525,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123989693</v>
+        <v>123988405</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480384</v>
+        <v>480313</v>
       </c>
       <c r="R10" t="n">
-        <v>6596389</v>
+        <v>6596806</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1595,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,12 +1605,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Badgrop.</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,69 +1632,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123987592</v>
+        <v>128335979</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480404</v>
+        <v>480430</v>
       </c>
       <c r="R11" t="n">
-        <v>6596699</v>
+        <v>6596771</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,22 +1697,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,64 +1739,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987670</v>
+        <v>129521781</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480411</v>
+        <v>480370</v>
       </c>
       <c r="R12" t="n">
-        <v>6596749</v>
+        <v>6596683</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,27 +1804,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,55 +1846,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123987786</v>
+        <v>129522031</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480379</v>
+        <v>480331</v>
       </c>
       <c r="R13" t="n">
-        <v>6596690</v>
+        <v>6596895</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,27 +1911,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,60 +1953,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123989116</v>
+        <v>129522042</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480299</v>
+        <v>480333</v>
       </c>
       <c r="R14" t="n">
-        <v>6596637</v>
+        <v>6596894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,27 +2018,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,64 +2060,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987555</v>
+        <v>129522083</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480411</v>
+        <v>480299</v>
       </c>
       <c r="R15" t="n">
-        <v>6596690</v>
+        <v>6596831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,27 +2125,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,64 +2167,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123988025</v>
+        <v>129522408</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480363</v>
+        <v>480284</v>
       </c>
       <c r="R16" t="n">
-        <v>6596775</v>
+        <v>6596815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2428,27 +2232,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökande på gran.</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2475,48 +2274,51 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338048</v>
+        <v>130799130</v>
       </c>
       <c r="B17" t="n">
-        <v>79743</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480316</v>
+        <v>480368</v>
       </c>
       <c r="R17" t="n">
-        <v>6596309</v>
+        <v>6596877</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2540,22 +2342,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2564,85 +2356,70 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128334100</v>
+        <v>130799135</v>
       </c>
       <c r="B18" t="n">
-        <v>56913</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480592</v>
+        <v>480353</v>
       </c>
       <c r="R18" t="n">
-        <v>6596494</v>
+        <v>6596838</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2666,27 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Uppflog av ung tjädertupp.</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2695,80 +2457,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128337422</v>
+        <v>130799138</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480328</v>
+        <v>480455</v>
       </c>
       <c r="R19" t="n">
-        <v>6596868</v>
+        <v>6596726</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2792,22 +2544,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,66 +2558,70 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129521348</v>
+        <v>130799271</v>
       </c>
       <c r="B20" t="n">
-        <v>92919</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480472</v>
+        <v>480454</v>
       </c>
       <c r="R20" t="n">
-        <v>6596483</v>
+        <v>6596712</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2899,22 +2645,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2923,66 +2659,70 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129521288</v>
+        <v>130799279</v>
       </c>
       <c r="B21" t="n">
-        <v>92919</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480473</v>
+        <v>480422</v>
       </c>
       <c r="R21" t="n">
-        <v>6596476</v>
+        <v>6596777</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3006,22 +2746,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3030,66 +2760,70 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129521154</v>
+        <v>130799291</v>
       </c>
       <c r="B22" t="n">
-        <v>92919</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480481</v>
+        <v>480423</v>
       </c>
       <c r="R22" t="n">
-        <v>6596464</v>
+        <v>6596768</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3113,22 +2847,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,32 +2861,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129522083</v>
+        <v>130799300</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3184,19 +2909,22 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480299</v>
+        <v>480424</v>
       </c>
       <c r="R23" t="n">
-        <v>6596831</v>
+        <v>6596768</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3220,22 +2948,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3244,32 +2962,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129522042</v>
+        <v>131809976</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3293,14 +3012,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480333</v>
+        <v>480301</v>
       </c>
       <c r="R24" t="n">
-        <v>6596894</v>
+        <v>6596807</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3327,22 +3046,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3369,14 +3088,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129521781</v>
+        <v>131810081</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3400,14 +3119,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480370</v>
+        <v>480313</v>
       </c>
       <c r="R25" t="n">
-        <v>6596683</v>
+        <v>6596805</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,22 +3153,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3476,45 +3195,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129521873</v>
+        <v>132346363</v>
       </c>
       <c r="B26" t="n">
-        <v>97411</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Runkabohöjd, Runkabohöjd, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480377</v>
+        <v>480191</v>
       </c>
       <c r="R26" t="n">
-        <v>6596794</v>
+        <v>6596748</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3541,22 +3260,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3583,10 +3302,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129522031</v>
+        <v>122335149</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,37 +3313,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480331</v>
+        <v>480442</v>
       </c>
       <c r="R27" t="n">
-        <v>6596895</v>
+        <v>6596485</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3648,22 +3370,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3672,28 +3384,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129522408</v>
+        <v>128338048</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,34 +3414,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480284</v>
+        <v>480316</v>
       </c>
       <c r="R28" t="n">
-        <v>6596815</v>
+        <v>6596309</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3755,22 +3468,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,10 +3510,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129521667</v>
+        <v>131813043</v>
       </c>
       <c r="B29" t="n">
-        <v>56921</v>
+        <v>79992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,48 +3521,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärn, Lilltjärn, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480457</v>
+        <v>480308</v>
       </c>
       <c r="R29" t="n">
-        <v>6596668</v>
+        <v>6596608</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3876,22 +3575,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3918,10 +3617,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129522345</v>
+        <v>131813198</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>79992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3929,53 +3628,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480276</v>
+        <v>480351</v>
       </c>
       <c r="R30" t="n">
-        <v>6596837</v>
+        <v>6596553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4002,27 +3682,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Framlockade. Fotografier.</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4049,64 +3724,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129524102</v>
+        <v>123987786</v>
       </c>
       <c r="B31" t="n">
-        <v>57898</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480493</v>
+        <v>480379</v>
       </c>
       <c r="R31" t="n">
-        <v>6596518</v>
+        <v>6596690</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4133,27 +3794,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Framlockade tillsammans med tofsmes. Video.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4180,51 +3841,58 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130799135</v>
+        <v>123989116</v>
       </c>
       <c r="B32" t="n">
-        <v>79243</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480353</v>
+        <v>480299</v>
       </c>
       <c r="R32" t="n">
-        <v>6596838</v>
+        <v>6596637</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4248,12 +3916,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4262,56 +3945,55 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131355405</v>
+        <v>131808004</v>
       </c>
       <c r="B33" t="n">
-        <v>58073</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4319,27 +4001,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stora Bergtjärn, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480466</v>
+        <v>480375</v>
       </c>
       <c r="R33" t="n">
-        <v>6596567</v>
+        <v>6596722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4366,22 +4042,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bohål i tallöverståndare lämpliga för pärluggla.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,45 +4089,59 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131812897</v>
+        <v>123987555</v>
       </c>
       <c r="B34" t="n">
-        <v>91855</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480272</v>
+        <v>480411</v>
       </c>
       <c r="R34" t="n">
-        <v>6596657</v>
+        <v>6596690</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4473,22 +4168,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4515,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131810081</v>
+        <v>123987670</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,34 +4226,48 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480313</v>
+        <v>480411</v>
       </c>
       <c r="R35" t="n">
-        <v>6596805</v>
+        <v>6596749</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4580,22 +4294,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4622,10 +4341,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131813198</v>
+        <v>123988025</v>
       </c>
       <c r="B36" t="n">
-        <v>79936</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,34 +4352,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480351</v>
+        <v>480363</v>
       </c>
       <c r="R36" t="n">
-        <v>6596553</v>
+        <v>6596775</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4687,22 +4420,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4729,10 +4467,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131813043</v>
+        <v>130799341</v>
       </c>
       <c r="B37" t="n">
-        <v>79936</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4740,37 +4478,49 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480308</v>
+        <v>480424</v>
       </c>
       <c r="R37" t="n">
-        <v>6596608</v>
+        <v>6596768</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4794,29 +4544,24 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>spår av barkfläkning på döende tall. Troligen tretåig hackspett</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4824,22 +4569,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131809976</v>
+        <v>130799375</v>
       </c>
       <c r="B38" t="n">
-        <v>79317</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4847,37 +4592,61 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480301</v>
+        <v>480400</v>
       </c>
       <c r="R38" t="n">
-        <v>6596807</v>
+        <v>6596779</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4901,22 +4670,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:11</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:11</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>knackade på gran i slänten lyckades tillslut se den och det var en hona.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4931,22 +4695,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131811868</v>
+        <v>131810287</v>
       </c>
       <c r="B39" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4992,10 +4756,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480325</v>
+        <v>480265</v>
       </c>
       <c r="R39" t="n">
-        <v>6596655</v>
+        <v>6596773</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5027,7 +4791,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5037,12 +4801,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringbarkning i död tall med fläkbark.</t>
+          <t>Ringbarkning i sakta döende tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,10 +4833,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131813900</v>
+        <v>131810858</v>
       </c>
       <c r="B40" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +4873,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5118,10 +4882,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480353</v>
+        <v>480328</v>
       </c>
       <c r="R40" t="n">
-        <v>6596484</v>
+        <v>6596728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5153,7 +4917,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5163,12 +4927,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringbarkning i nyligen död tall med fläkbark.</t>
+          <t>Färska spår av födosök i sakta döende stavatall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5195,32 +4959,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131810538</v>
+        <v>131811868</v>
       </c>
       <c r="B41" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5233,14 +4997,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5249,10 +5008,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480263</v>
+        <v>480325</v>
       </c>
       <c r="R41" t="n">
-        <v>6596738</v>
+        <v>6596655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5284,7 +5043,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5294,12 +5053,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På grov tallåga.</t>
+          <t>Ringbarkning i död tall med fläkbark.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5326,10 +5085,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131808004</v>
+        <v>131813794</v>
       </c>
       <c r="B42" t="n">
-        <v>57950</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5337,16 +5096,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5366,7 +5125,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5375,10 +5134,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480375</v>
+        <v>480353</v>
       </c>
       <c r="R42" t="n">
-        <v>6596722</v>
+        <v>6596484</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5410,7 +5169,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5420,12 +5179,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare lämpliga för pärluggla.</t>
+          <t>Ringbarkning i torraka med fläkbark (nyligen omkullblåst).</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5452,32 +5211,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131810287</v>
+        <v>122335180</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5490,24 +5249,30 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480265</v>
+        <v>480403</v>
       </c>
       <c r="R43" t="n">
-        <v>6596773</v>
+        <v>6596616</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5531,27 +5296,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:21</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringbarkning i sakta döende tall.</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5566,71 +5316,72 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131810858</v>
+        <v>123989672</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480328</v>
+        <v>480384</v>
       </c>
       <c r="R44" t="n">
-        <v>6596728</v>
+        <v>6596389</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5657,27 +5408,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök i sakta döende stavatall.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5707,7 +5453,7 @@
         <v>131806959</v>
       </c>
       <c r="B45" t="n">
-        <v>57141</v>
+        <v>57162</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5830,37 +5576,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131807177</v>
+        <v>131810538</v>
       </c>
       <c r="B46" t="n">
-        <v>58114</v>
+        <v>57162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5870,25 +5616,24 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480453</v>
+        <v>480263</v>
       </c>
       <c r="R46" t="n">
-        <v>6596568</v>
+        <v>6596738</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5920,7 +5665,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5930,12 +5675,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Filmsnutt finns sparad.</t>
+          <t>På grov tallåga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5965,7 +5710,7 @@
         <v>131814360</v>
       </c>
       <c r="B47" t="n">
-        <v>57141</v>
+        <v>57162</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6088,10 +5833,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133024889</v>
+        <v>128336665</v>
       </c>
       <c r="B48" t="n">
-        <v>91891</v>
+        <v>5179</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6099,34 +5844,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480357</v>
+        <v>480392</v>
       </c>
       <c r="R48" t="n">
-        <v>6596841</v>
+        <v>6596824</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6153,22 +5898,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6192,6 +5937,2129 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129521667</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>480457</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6596668</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123987592</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>480404</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6596699</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128337422</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>480328</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6596868</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129522345</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>480276</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6596837</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Framlockade. Fotografier.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131355405</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>480466</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6596567</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131807177</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>480453</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6596568</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Filmsnutt finns sparad.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122335205</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79486</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>480539</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6596612</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129521154</v>
+      </c>
+      <c r="B56" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>480481</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6596464</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129524027</v>
+      </c>
+      <c r="B57" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>480490</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6596448</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128335285</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>480549</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6596634</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128335348</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lilltjärn, Lilltjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>480538</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6596657</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130799121</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>480607</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6596563</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122335213</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>480554</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6596596</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123991709</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>480553</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6596500</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128334100</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>480592</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6596494</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Uppflog av ung tjädertupp.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131806920</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>480482</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6596430</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131815416</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>480484</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6596445</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129524102</v>
+      </c>
+      <c r="B66" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>480493</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6596518</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Framlockade tillsammans med tofsmes. Video.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51567-2025 artfynd.xlsx
+++ b/artfynd/A 51567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122335159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122335205</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521873</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131812897</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133024889</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62161729</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521154</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521288</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521331</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1738,6 +1788,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524027</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,6 +1905,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123987634</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988405</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2064,6 +2129,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128335285</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2171,6 +2241,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128335348</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2278,6 +2353,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128335979</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2385,6 +2465,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521781</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2492,6 +2577,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522031</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2599,6 +2689,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522042</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2706,6 +2801,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522083</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2813,6 +2913,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522408</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799121</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3015,6 +3125,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799130</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3116,6 +3231,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799135</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3217,6 +3337,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799138</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3318,6 +3443,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799271</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3419,6 +3549,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799279</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3520,6 +3655,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799291</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3621,6 +3761,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799300</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3728,6 +3873,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809976</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3835,6 +3985,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131810081</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3942,6 +4097,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346363</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4043,6 +4203,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122335149</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4144,6 +4309,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122335213</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4251,6 +4421,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123991709</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4358,6 +4533,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128338048</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4465,6 +4645,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131813043</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4572,6 +4757,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131813198</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4689,6 +4879,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123987786</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4811,6 +5006,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123989116</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4937,6 +5137,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808004</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5063,6 +5268,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123987555</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5189,6 +5399,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123987670</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5315,6 +5530,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5429,6 +5649,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799341</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5555,6 +5780,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799375</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5681,6 +5911,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131810287</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5807,6 +6042,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131810858</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5933,6 +6173,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131811868</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6059,6 +6304,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131813794</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6176,6 +6426,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122335180</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6298,6 +6553,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123989672</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6429,6 +6689,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128334100</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6555,6 +6820,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806920</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6681,6 +6951,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806959</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6812,6 +7087,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131810538</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6938,6 +7218,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131814360</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7064,6 +7349,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131815416</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7171,6 +7461,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128336665</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7292,6 +7587,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521667</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7418,6 +7718,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123987592</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7539,6 +7844,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128337422</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7670,6 +7980,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522345</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7801,6 +8116,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524102</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7928,6 +8248,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131355405</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8060,8 +8385,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131807177</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>